--- a/fixtures/review.xlsx
+++ b/fixtures/review.xlsx
@@ -14,8 +14,8 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:authors>
-    <x:author>tc={41BFF466-8DFE-4C62-8EB0-C9936ADC79D8}</x:author>
-    <x:author>tc={8F571583-47F0-4151-8F7D-7DC48669ECC3}</x:author>
+    <x:author>tc={38C637D7-C79C-43B3-8A03-41F0E7E446AF}</x:author>
+    <x:author>tc={BBB2A8A7-08AF-4001-BB26-C3FC0F313DF9}</x:author>
   </x:authors>
   <x:commentList>
     <x:comment ref="B2" authorId="0">
@@ -139,8 +139,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Reviewer A" id="{C7C85389-4F5E-427B-B1A5-DAACA6FAB53A}" userId="Reviewer A" providerId="None"/>
-  <xltc:person displayName="Reviewer B" id="{35053FFC-4F94-47F2-AEF7-F16911AED4FC}" userId="Reviewer B" providerId="None"/>
+  <xltc:person displayName="Reviewer A" id="{52D9DDDB-AD44-4CFD-AF47-F032CF730657}" userId="Reviewer A" providerId="None"/>
+  <xltc:person displayName="Reviewer B" id="{C26F7ABD-FB83-47E7-8EE8-2D411760F12A}" userId="Reviewer B" providerId="None"/>
 </xltc:personList>
 </file>
 
@@ -429,10 +429,10 @@
 
 <file path=xl/threadedcomments/threadedcomment.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:ThreadedComments xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:threadedComment ref="B2" dT="2026-04-20T10:39:57.3587693Z" personId="{C7C85389-4F5E-427B-B1A5-DAACA6FAB53A}" id="{41BFF466-8DFE-4C62-8EB0-C9936ADC79D8}" done="1">
+  <xltc:threadedComment ref="B2" dT="2026-04-20T15:23:28.7838911Z" personId="{52D9DDDB-AD44-4CFD-AF47-F032CF730657}" id="{38C637D7-C79C-43B3-8A03-41F0E7E446AF}" done="1">
     <xltc:text>Initial balance confirmed</xltc:text>
   </xltc:threadedComment>
-  <xltc:threadedComment ref="C2" dT="2026-04-20T10:39:57.3588477Z" personId="{35053FFC-4F94-47F2-AEF7-F16911AED4FC}" id="{8F571583-47F0-4151-8F7D-7DC48669ECC3}" done="0">
+  <xltc:threadedComment ref="C2" dT="2026-04-20T15:23:28.7839673Z" personId="{C26F7ABD-FB83-47E7-8EE8-2D411760F12A}" id="{BBB2A8A7-08AF-4001-BB26-C3FC0F313DF9}" done="0">
     <xltc:text>Needs follow-up on Q3 close</xltc:text>
   </xltc:threadedComment>
 </xltc:ThreadedComments>
